--- a/public/examples/sime-darby-malaysia-pnl-fy2025-fy2026q3.xlsx
+++ b/public/examples/sime-darby-malaysia-pnl-fy2025-fy2026q3.xlsx
@@ -113,7 +113,7 @@
     <t>Gross margin is the published annual margin applied evenly; opex ratios (4.5/5.5/1.4/0.9% of revenue) are back-solved from published operating income.</t>
   </si>
   <si>
-    <t>The monthly split inside each quarter is synthesized (30/33/37%) — the group reports quarterly only. Not audited monthly accounts.</t>
+    <t>The monthly split inside each quarter is synthesized (30/33/37%). Not audited monthly accounts.</t>
   </si>
   <si>
     <t>No Units column: a diversified industrial/motors group has no single volume metric, so price/volume/mix will not run.</t>
@@ -506,7 +506,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="8" width="20" style="1" customWidth="1"/>
+    <col min="2" max="8" width="22" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1092,7 +1092,7 @@
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="110" customWidth="1"/>
+    <col min="1" max="1" width="120" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
